--- a/output/graficos_dimensiones/comunal_e_mat_a_2023_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_e_mat_a_2023_arica y parinacota.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 21:42</t>
+    <t xml:space="preserve">2026-09-10 00:51</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_mat_a_2023_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_e_mat_a_2023_arica y parinacota.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 00:51</t>
+    <t xml:space="preserve">2026-09-18 11:00</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
